--- a/files/港岛-坚尼地城-Kennedy 38.xlsx
+++ b/files/港岛-坚尼地城-Kennedy 38.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kennedy 38 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -757,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -803,7 +661,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -849,7 +707,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -895,7 +753,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -941,7 +799,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1033,7 +891,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1079,7 +937,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1125,7 +983,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1171,7 +1029,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1217,7 +1075,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1309,7 +1167,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1401,7 +1259,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1497,7 +1355,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1543,7 +1401,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1589,7 +1447,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1635,7 +1493,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1681,7 +1539,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1727,7 +1585,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1773,7 +1631,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1819,7 +1677,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1911,7 +1769,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1957,7 +1815,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2003,7 +1861,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2099,7 +1957,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2145,7 +2003,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2191,7 +2049,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2237,7 +2095,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2283,7 +2141,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2375,7 +2233,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2421,7 +2279,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2513,7 +2371,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-27</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2559,7 +2417,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2605,7 +2463,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2701,7 +2559,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2747,7 +2605,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2793,7 +2651,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2839,7 +2697,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2885,7 +2743,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2931,7 +2789,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2977,7 +2835,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3023,7 +2881,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3115,7 +2973,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3161,7 +3019,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-03</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3207,7 +3065,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3303,7 +3161,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3349,7 +3207,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3395,7 +3253,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3441,7 +3299,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3487,7 +3345,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-28</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3533,7 +3391,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3579,7 +3437,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3625,7 +3483,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3671,7 +3529,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3717,7 +3575,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3763,7 +3621,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3809,7 +3667,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3905,7 +3763,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3951,7 +3809,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3997,7 +3855,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4043,7 +3901,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4089,7 +3947,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4181,7 +4039,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4227,7 +4085,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4319,7 +4177,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4365,7 +4223,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4411,7 +4269,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4507,7 +4365,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4553,7 +4411,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4599,7 +4457,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4645,7 +4503,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4691,7 +4549,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4737,7 +4595,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4783,7 +4641,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4829,7 +4687,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-08</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4921,7 +4779,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4967,7 +4825,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5013,7 +4871,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5109,7 +4967,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5155,7 +5013,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5201,7 +5059,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5247,7 +5105,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5293,7 +5151,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5339,7 +5197,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5385,7 +5243,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5477,7 +5335,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5523,7 +5381,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5569,7 +5427,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5615,7 +5473,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5711,7 +5569,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5757,7 +5615,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5803,7 +5661,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5849,7 +5707,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5895,7 +5753,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5941,7 +5799,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5987,7 +5845,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6033,7 +5891,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6079,7 +5937,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6125,7 +5983,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6171,7 +6029,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6217,7 +6075,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6313,7 +6171,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6359,7 +6217,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6405,7 +6263,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6451,7 +6309,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6497,7 +6355,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6543,7 +6401,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6589,7 +6447,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6635,7 +6493,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6681,7 +6539,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6727,7 +6585,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6773,7 +6631,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6819,7 +6677,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-19</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6915,7 +6773,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6961,7 +6819,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7007,7 +6865,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7053,7 +6911,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7099,7 +6957,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7145,7 +7003,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7191,7 +7049,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7237,7 +7095,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7283,7 +7141,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7329,7 +7187,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7375,7 +7233,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7421,7 +7279,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7517,7 +7375,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7563,7 +7421,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7609,7 +7467,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7701,7 +7559,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7747,7 +7605,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7793,7 +7651,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7839,7 +7697,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7885,7 +7743,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7931,7 +7789,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7977,7 +7835,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8023,7 +7881,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8119,7 +7977,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8165,7 +8023,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8257,7 +8115,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8303,7 +8161,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8349,7 +8207,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8395,7 +8253,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8441,7 +8299,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8487,7 +8345,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8533,7 +8391,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8579,7 +8437,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8721,7 +8579,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8767,7 +8625,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8813,7 +8671,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8859,7 +8717,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8905,7 +8763,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -8951,7 +8809,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -8997,7 +8855,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9043,7 +8901,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9089,7 +8947,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9135,7 +8993,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9181,7 +9039,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9227,7 +9085,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9323,7 +9181,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9369,7 +9227,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9415,7 +9273,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9461,7 +9319,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9507,7 +9365,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9553,7 +9411,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9599,7 +9457,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9645,7 +9503,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9691,7 +9549,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9737,7 +9595,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9783,7 +9641,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-21</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9829,7 +9687,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9925,7 +9783,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -9971,7 +9829,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10017,7 +9875,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10063,7 +9921,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10109,7 +9967,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10155,7 +10013,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10201,7 +10059,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10247,7 +10105,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10293,7 +10151,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10339,7 +10197,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10385,7 +10243,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10431,7 +10289,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10527,7 +10385,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10573,7 +10431,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10619,7 +10477,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10665,7 +10523,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10711,7 +10569,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10757,7 +10615,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10803,7 +10661,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -10849,7 +10707,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10895,7 +10753,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10941,7 +10799,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -10987,7 +10845,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -11033,7 +10891,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11129,7 +10987,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11175,7 +11033,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11221,7 +11079,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11267,7 +11125,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11313,7 +11171,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11359,7 +11217,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11405,7 +11263,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11451,7 +11309,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11497,7 +11355,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11543,7 +11401,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11589,7 +11447,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11635,7 +11493,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11731,7 +11589,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11777,7 +11635,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -11823,7 +11681,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11869,7 +11727,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -11915,7 +11773,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -11961,7 +11819,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -12007,7 +11865,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -12099,7 +11957,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12145,7 +12003,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12191,7 +12049,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12237,7 +12095,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12333,7 +12191,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12379,7 +12237,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12425,7 +12283,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12471,7 +12329,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12517,7 +12375,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12563,7 +12421,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12609,7 +12467,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12655,7 +12513,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12701,7 +12559,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -12747,7 +12605,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -12793,7 +12651,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -12839,7 +12697,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -12935,7 +12793,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -12981,7 +12839,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -13027,7 +12885,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -13073,7 +12931,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -13119,7 +12977,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13165,7 +13023,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13211,7 +13069,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13257,7 +13115,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13349,7 +13207,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -13395,7 +13253,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-19</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -13441,7 +13299,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -13537,7 +13395,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-28</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13583,7 +13441,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -13629,7 +13487,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13675,7 +13533,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -13721,7 +13579,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -13767,7 +13625,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -13813,7 +13671,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -13859,7 +13717,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -13905,7 +13763,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -13951,7 +13809,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-22</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -13997,7 +13855,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-11</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -14043,7 +13901,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14139,7 +13997,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14185,7 +14043,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -14231,7 +14089,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14277,7 +14135,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14323,7 +14181,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -14369,7 +14227,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14415,7 +14273,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -14461,7 +14319,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -14553,7 +14411,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14599,7 +14457,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14645,7 +14503,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -14741,7 +14599,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -14787,7 +14645,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -14833,7 +14691,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -14879,7 +14737,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -14925,7 +14783,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -14971,7 +14829,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-19</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -15017,7 +14875,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -15063,7 +14921,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -15109,7 +14967,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15155,7 +15013,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -15201,7 +15059,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -15247,7 +15105,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -15339,7 +15197,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -15385,7 +15243,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -15431,7 +15289,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -15477,7 +15335,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -15523,7 +15381,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -15569,7 +15427,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -15615,7 +15473,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -15661,7 +15519,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -15707,7 +15565,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -15753,7 +15611,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -15799,7 +15657,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -15845,7 +15703,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -15941,7 +15799,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -15987,7 +15845,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -16033,7 +15891,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -16079,7 +15937,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -16125,7 +15983,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -16171,7 +16029,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -16217,7 +16075,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -16309,7 +16167,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -16355,7 +16213,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-02</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -16477,3108 +16335,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kennedy 38 - Kennedy 38 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>341 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>304 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>25 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1000呎 (4+房)
-$4,300万
-$43,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 566呎 (2房)
-$2,434万
-$43,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 796呎 (3房)
-$3,224万
-$40,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 880呎 (3房)
-$3,524万
-$40,045/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr"/>
-      <c r="M6" s="17" t="inlineStr"/>
-      <c r="N6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$951万
-$33,136/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,520万
-$33,341/呎
-(23年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$1,035万
-$31,164/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$990万
-$37,775/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$811万
-$30,617/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$902万
-$30,896/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$742万
-$32,526/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$890万
-$30,909/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$870万
-$29,208/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$973万
-$32,206/呎
-(21年-11月)</t>
-        </is>
-      </c>
-      <c r="M7" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$963万
-$32,870/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N7" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$962万
-$32,074/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$946万
-$32,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,468万
-$32,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$1,030万
-$31,009/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$985万
-$37,592/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$806万
-$30,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$898万
-$30,742/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$740万
-$32,471/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$886万
-$30,759/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$885万
-$29,609/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$968万
-$32,057/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$958万
-$32,707/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N8" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$957万
-$31,809/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$921万
-$32,214/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,433万
-$31,421/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
-$1,047万
-$31,448/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$980万
-$37,397/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$803万
-$30,315/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$893万
-$30,591/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>H | 229呎 (开放式)
-$859万
-$37,528/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$882万
-$30,609/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$881万
-$29,560/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$964万
-$31,904/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$954万
-$32,544/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$932万
-$31,065/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$932万
-$32,594/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,408万
-$30,876/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$1,019万
-$30,703/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$975万
-$37,214/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$799万
-$30,162/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$889万
-$30,437/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$733万
-$32,147/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$877万
-$30,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$877万
-$29,415/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$959万
-$31,755/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$949万
-$32,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$948万
-$31,599/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$917万
-$31,948/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,357万
-$29,761/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$1,019万
-$30,703/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$876万
-$33,454/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$817万
-$30,949/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$889万
-$30,437/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$770万
-$33,758/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$877万
-$30,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$877万
-$29,415/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$959万
-$31,755/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$949万
-$32,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$948万
-$31,494/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$907万
-$31,717/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,339万
-$29,366/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
-$1,011万
-$30,370/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$965万
-$36,847/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$791万
-$29,843/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$880万
-$30,135/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>H | 229呎 (开放式)
-$838万
-$36,616/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$869万
-$30,168/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$852万
-$28,511/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$934万
-$30,924/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$939万
-$32,059/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$938万
-$31,283/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$903万
-$31,563/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,365万
-$29,928/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$1,019万
-$30,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$960万
-$36,660/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$804万
-$30,353/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$875万
-$29,965/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$726万
-$31,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$841万
-$29,203/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$830万
-$27,846/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$909万
-$30,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$935万
-$31,899/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$934万
-$31,130/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$898万
-$31,302/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,391万
-$30,511/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$1,013万
-$30,526/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$779万
-$29,717/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$796万
-$30,054/呎
-(21年-11月)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$866万
-$29,641/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$711万
-$31,164/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$819万
-$28,428/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$826万
-$27,710/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$925万
-$30,634/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="inlineStr">
-        <is>
-          <t>M | 292呎 (1房)
-$941万
-$32,219/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$929万
-$30,870/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$894万
-$31,149/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,367万
-$29,975/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$1,008万
-$30,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$775万
-$29,569/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$792万
-$29,905/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$861万
-$29,497/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$687万
-$30,146/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$833万
-$28,916/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$840万
-$28,183/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$921万
-$30,488/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$916万
-$31,254/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$925万
-$30,718/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$885万
-$30,826/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,323万
-$29,015/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$992万
-$29,865/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$771万
-$29,422/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$771万
-$29,219/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$857万
-$29,349/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$684万
-$29,996/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$829万
-$28,769/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$836万
-$27,947/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$867万
-$28,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M16" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$888万
-$30,311/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N16" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$907万
-$30,231/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$883万
-$30,767/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,294万
-$28,370/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$989万
-$29,797/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$767万
-$29,277/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$785万
-$29,610/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$872万
-$29,853/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$680万
-$29,846/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$824万
-$28,628/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$831万
-$27,902/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$846万
-$28,017/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$870万
-$29,706/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N17" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$894万
-$29,690/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$879万
-$30,616/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,290万
-$28,285/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$953万
-$28,705/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$801万
-$30,586/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$764万
-$28,930/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$863万
-$29,540/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$677万
-$29,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$802万
-$27,847/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$809万
-$27,142/呎
-(21年-11月)</t>
-        </is>
-      </c>
-      <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$842万
-$27,877/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M18" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$866万
-$29,559/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N18" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$870万
-$28,902/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$874万
-$30,469/呎
-(21年-11月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,354万
-$29,692/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$969万
-$29,199/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$797万
-$30,435/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$777万
-$29,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$844万
-$28,911/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$674万
-$29,550/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$816万
-$28,325/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$823万
-$27,517/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$820万
-$27,137/呎
-(21年-11月)</t>
-        </is>
-      </c>
-      <c r="M19" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$862万
-$29,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N19" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$885万
-$29,495/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$855万
-$29,807/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,354万
-$29,692/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$969万
-$29,199/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$797万
-$30,435/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$777万
-$29,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$844万
-$28,911/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$694万
-$30,438/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$816万
-$28,325/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$823万
-$27,609/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$838万
-$27,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$862万
-$29,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N20" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$885万
-$29,397/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$844万
-$29,523/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,313万
-$28,788/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$965万
-$29,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$786万
-$29,992/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$746万
-$28,264/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$816万
-$27,949/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$664万
-$29,112/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$789万
-$27,408/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$810万
-$27,104/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$825万
-$27,326/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M21" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$824万
-$28,115/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N21" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$855万
-$28,398/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$822万
-$28,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,309万
-$28,703/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$950万
-$28,620/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$730万
-$27,859/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$730万
-$27,557/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$812万
-$27,811/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$646万
-$28,354/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$785万
-$27,271/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$806万
-$26,969/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L22" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$821万
-$27,189/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M22" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$835万
-$28,499/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N22" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$850万
-$28,348/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$818万
-$28,493/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,295万
-$28,399/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$945万
-$28,476/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$789万
-$30,116/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$743万
-$28,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$808万
-$27,672/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$644万
-$28,255/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$781万
-$27,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$802万
-$26,924/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$799万
-$26,467/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$819万
-$27,949/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N23" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$846万
-$28,113/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$832万
-$29,083/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,291万
-$28,312/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
-$951万
-$28,556/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$723万
-$27,581/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$739万
-$27,888/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$804万
-$27,533/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$640万
-$28,069/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$778万
-$26,999/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$798万
-$26,791/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L24" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$813万
-$26,918/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M24" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$819万
-$27,940/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N24" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$842万
-$27,973/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$828万
-$28,837/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,287万
-$28,227/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
-$916万
-$27,497/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$735万
-$28,053/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$719万
-$27,146/呎
-(21年-11月)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$800万
-$27,395/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$652万
-$28,596/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$774万
-$26,865/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$794万
-$26,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$809万
-$26,783/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>M | 292呎 (1房)
-$814万
-$27,875/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N25" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$838万
-$27,925/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$815万
-$28,510/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,287万
-$28,220/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
-$927万
-$27,829/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$715万
-$27,306/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$732万
-$27,715/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$796万
-$27,259/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 229呎 (开放式)
-$649万
-$28,327/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$770万
-$26,728/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$790万
-$26,434/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L26" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$805万
-$26,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M26" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$804万
-$27,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N26" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$825万
-$27,511/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$815万
-$28,510/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,287万
-$28,220/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$927万
-$27,913/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$950万
-$36,248/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$732万
-$27,715/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$752万
-$25,761/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$649万
-$28,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$770万
-$26,728/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$790万
-$26,522/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L27" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$805万
-$26,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$804万
-$27,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N27" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$825万
-$27,420/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$807万
-$28,227/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,311万
-$28,747/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
-$908万
-$27,254/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$701万
-$26,766/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$724万
-$27,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$761万
-$26,072/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>H | 229呎 (开放式)
-$628万
-$27,436/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$762万
-$26,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K28" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$782万
-$26,257/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L28" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$797万
-$26,384/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M28" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$799万
-$27,258/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N28" s="16" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$817万
-$27,148/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$804万
-$28,118/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,265万
-$27,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$914万
-$27,533/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$948万
-$36,198/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$721万
-$27,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$758万
-$25,942/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 229呎 (开放式)
-$638万
-$27,881/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$742万
-$25,759/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$762万
-$25,474/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L29" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$793万
-$26,253/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M29" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$810万
-$27,631/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N29" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$813万
-$27,100/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-$724万
-$27,838/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$781万
-$27,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,248万
-$27,368/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
-$898万
-$26,981/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$709万
-$27,063/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$701万
-$26,446/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$753万
-$25,785/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$635万
-$27,834/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$754万
-$26,172/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K30" s="16" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$757万
-$25,320/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L30" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$788万
-$26,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M30" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$794万
-$27,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N30" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$809万
-$26,965/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$778万
-$27,217/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1,248万
-$27,365/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
-$894万
-$26,846/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$690万
-$26,340/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$697万
-$26,314/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$750万
-$25,675/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>H | 229呎 (开放式)
-$632万
-$27,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$750万
-$26,041/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$770万
-$25,840/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L31" s="16" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$784万
-$25,964/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M31" s="16" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$792万
-$27,015/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N31" s="16" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$805万
-$26,830/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 238呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>B | 687呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-$947万
-$30,638/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 240呎 (开放式)
-$756万
-$31,502/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 243呎 (开放式)
-$804万
-$33,100/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 270呎 (1房)
-$814万
-$30,130/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 207呎 (开放式)
-$637万
-$30,765/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>H | 267呎 (1房)
-$763万
-$28,561/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>J | 278呎 (1房)
-$802万
-$28,861/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K32" s="16" t="inlineStr">
-        <is>
-          <t>K | 279呎 (1房)
-$859万
-$30,799/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L32" s="16" t="inlineStr">
-        <is>
-          <t>L | 271呎 (1房)
-$964万
-$35,587/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M32" s="16" t="inlineStr">
-        <is>
-          <t>M | 279呎 (1房)
-$904万
-$32,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N32" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-坚尼地城-Kennedy 38.xlsx
+++ b/files/港岛-坚尼地城-Kennedy 38.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kennedy 38" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +153,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +234,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +670,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -16335,4 +16531,3108 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Kennedy 38 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1000呎 (4+房)
+$4300万
+$43,000/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 566呎 (2房)
+$2434万
+$43,000/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 796呎 (3房)
+$3224万
+$40,500/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 880呎 (3房)
+$3524万
+$40,045/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+      <c r="K5" s="21" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr"/>
+      <c r="M5" s="21" t="inlineStr"/>
+      <c r="N5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$951万
+$33,136/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1520万
+$33,341/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$1035万
+$31,164/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$990万
+$37,775/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$811万
+$30,617/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$902万
+$30,896/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$742万
+$32,526/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$890万
+$30,909/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$870万
+$29,208/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$973万
+$32,206/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$963万
+$32,870/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$962万
+$32,074/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$946万
+$32,976/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1468万
+$32,200/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$1030万
+$31,009/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$985万
+$37,592/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$806万
+$30,426/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$898万
+$30,742/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$740万
+$32,471/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$886万
+$30,759/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$885万
+$29,609/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$968万
+$32,057/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$958万
+$32,707/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$957万
+$31,809/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$921万
+$32,214/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1433万
+$31,421/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$1047万
+$31,448/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$980万
+$37,397/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$803万
+$30,315/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$893万
+$30,591/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>H | 229呎 (开放式)
+$859万
+$37,528/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$882万
+$30,609/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$881万
+$29,560/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$964万
+$31,904/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$954万
+$32,544/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$932万
+$31,065/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$932万
+$32,594/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1408万
+$30,876/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$1019万
+$30,703/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$975万
+$37,214/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$799万
+$30,162/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$889万
+$30,437/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$733万
+$32,147/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$877万
+$30,462/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$877万
+$29,415/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$959万
+$31,755/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$949万
+$32,382/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$948万
+$31,599/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$917万
+$31,948/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1357万
+$29,761/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$1019万
+$30,703/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$876万
+$33,454/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$817万
+$30,949/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$889万
+$30,437/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$770万
+$33,758/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$877万
+$30,462/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$877万
+$29,415/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$959万
+$31,755/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$949万
+$32,382/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$948万
+$31,494/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$907万
+$31,717/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1339万
+$29,366/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$1011万
+$30,370/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$965万
+$36,847/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$791万
+$29,843/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$880万
+$30,135/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>H | 229呎 (开放式)
+$838万
+$36,616/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$869万
+$30,168/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$852万
+$28,511/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$934万
+$30,924/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$939万
+$32,059/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$938万
+$31,283/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$903万
+$31,563/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1365万
+$29,928/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$1019万
+$30,679/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$960万
+$36,660/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$804万
+$30,353/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$875万
+$29,965/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$726万
+$31,839/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$841万
+$29,203/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$830万
+$27,846/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$909万
+$30,108/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$935万
+$31,899/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$934万
+$31,130/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$898万
+$31,302/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1391万
+$30,511/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$1013万
+$30,526/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$779万
+$29,717/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$796万
+$30,054/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$866万
+$29,641/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$711万
+$31,164/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$819万
+$28,428/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$826万
+$27,710/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$925万
+$30,634/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M13" s="20" t="inlineStr">
+        <is>
+          <t>M | 292呎 (1房)
+$941万
+$32,219/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$929万
+$30,870/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$894万
+$31,149/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1367万
+$29,975/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$1008万
+$30,374/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$775万
+$29,569/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$792万
+$29,905/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$861万
+$29,497/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$687万
+$30,146/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$833万
+$28,916/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$840万
+$28,183/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$921万
+$30,488/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M14" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$916万
+$31,254/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$925万
+$30,718/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$885万
+$30,826/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1323万
+$29,015/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$992万
+$29,865/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$771万
+$29,422/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$771万
+$29,219/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$857万
+$29,349/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$684万
+$29,996/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$829万
+$28,769/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$836万
+$27,947/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$867万
+$28,721/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$888万
+$30,311/呎
+(24年-02月)</t>
+        </is>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$907万
+$30,231/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$883万
+$30,767/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1294万
+$28,370/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$989万
+$29,797/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$767万
+$29,277/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$785万
+$29,610/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$872万
+$29,853/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$680万
+$29,846/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$824万
+$28,628/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$831万
+$27,902/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$846万
+$28,017/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$870万
+$29,706/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$894万
+$29,690/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$879万
+$30,616/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1290万
+$28,285/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$953万
+$28,705/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$801万
+$30,586/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$764万
+$28,930/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$863万
+$29,540/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$677万
+$29,700/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$802万
+$27,847/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$809万
+$27,142/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$842万
+$27,877/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M17" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$866万
+$29,559/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$870万
+$28,902/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$874万
+$30,469/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1354万
+$29,692/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$969万
+$29,199/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$797万
+$30,435/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$777万
+$29,426/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$844万
+$28,911/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$674万
+$29,550/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$816万
+$28,325/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$823万
+$27,517/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$820万
+$27,137/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$862万
+$29,411/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$885万
+$29,495/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$855万
+$29,807/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1354万
+$29,692/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$969万
+$29,199/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$797万
+$30,435/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$777万
+$29,426/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$844万
+$28,911/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$694万
+$30,438/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$816万
+$28,325/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$823万
+$27,609/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$838万
+$27,740/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$862万
+$29,411/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$885万
+$29,397/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$844万
+$29,523/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1313万
+$28,788/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$965万
+$29,071/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$786万
+$29,992/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$746万
+$28,264/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$816万
+$27,949/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$664万
+$29,112/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$789万
+$27,408/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$810万
+$27,104/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$825万
+$27,326/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M20" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$824万
+$28,115/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$855万
+$28,398/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$822万
+$28,637/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1309万
+$28,703/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$950万
+$28,620/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$730万
+$27,859/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$730万
+$27,557/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$812万
+$27,811/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$646万
+$28,354/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$785万
+$27,271/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$806万
+$26,969/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$821万
+$27,189/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M21" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$835万
+$28,499/呎
+(24年-02月)</t>
+        </is>
+      </c>
+      <c r="N21" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$850万
+$28,348/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$818万
+$28,493/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1295万
+$28,399/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$945万
+$28,476/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$789万
+$30,116/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$743万
+$28,030/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$808万
+$27,672/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$644万
+$28,255/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$781万
+$27,133/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$802万
+$26,924/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$799万
+$26,467/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M22" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$819万
+$27,949/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$846万
+$28,113/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$832万
+$29,083/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1291万
+$28,312/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$951万
+$28,556/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$723万
+$27,581/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$739万
+$27,888/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$804万
+$27,533/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$640万
+$28,069/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$778万
+$26,999/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$798万
+$26,791/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$813万
+$26,918/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M23" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$819万
+$27,940/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$842万
+$27,973/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$828万
+$28,837/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1287万
+$28,227/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$916万
+$27,497/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$735万
+$28,053/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$719万
+$27,146/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$800万
+$27,395/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$652万
+$28,596/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$774万
+$26,865/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$794万
+$26,655/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$809万
+$26,783/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="inlineStr">
+        <is>
+          <t>M | 292呎 (1房)
+$814万
+$27,875/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$838万
+$27,925/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$815万
+$28,510/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1287万
+$28,220/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$927万
+$27,829/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$715万
+$27,306/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$732万
+$27,715/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$796万
+$27,259/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 229呎 (开放式)
+$649万
+$28,327/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$770万
+$26,728/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$790万
+$26,434/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$805万
+$26,649/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$804万
+$27,424/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="N25" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$825万
+$27,511/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$815万
+$28,510/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1287万
+$28,220/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$927万
+$27,913/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$950万
+$36,248/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$732万
+$27,715/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$752万
+$25,761/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$649万
+$28,451/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$770万
+$26,728/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$790万
+$26,522/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$805万
+$26,649/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M26" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$804万
+$27,424/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$825万
+$27,420/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$807万
+$28,227/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1311万
+$28,747/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$908万
+$27,254/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$701万
+$26,766/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$724万
+$27,336/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$761万
+$26,072/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 229呎 (开放式)
+$628万
+$27,436/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$762万
+$26,462/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$782万
+$26,257/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$797万
+$26,384/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M27" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$799万
+$27,258/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$817万
+$27,148/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$804万
+$28,118/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1265万
+$27,739/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$914万
+$27,533/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$948万
+$36,198/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$721万
+$27,300/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$758万
+$25,942/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 229呎 (开放式)
+$638万
+$27,881/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$742万
+$25,759/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$762万
+$25,474/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$793万
+$26,253/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M28" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$810万
+$27,631/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="N28" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$813万
+$27,100/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+$724万
+$27,838/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$781万
+$27,226/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1248万
+$27,368/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$898万
+$26,981/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$709万
+$27,063/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$701万
+$26,446/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$753万
+$25,785/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$635万
+$27,834/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$754万
+$26,172/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$757万
+$25,320/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$788万
+$26,095/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M29" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$794万
+$27,095/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="N29" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$809万
+$26,965/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$778万
+$27,217/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1248万
+$27,365/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$894万
+$26,846/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$690万
+$26,340/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$697万
+$26,314/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$750万
+$25,675/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>H | 229呎 (开放式)
+$632万
+$27,600/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$750万
+$26,041/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$770万
+$25,840/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$784万
+$25,964/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="M30" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$792万
+$27,015/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$805万
+$26,830/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 238呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>B | 687呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+$947万
+$30,638/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 240呎 (开放式)
+$756万
+$31,502/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 243呎 (开放式)
+$804万
+$33,100/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 270呎 (1房)
+$814万
+$30,130/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 207呎 (开放式)
+$637万
+$30,765/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>H | 267呎 (1房)
+$763万
+$28,561/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$802万
+$28,861/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>K | 279呎 (1房)
+$859万
+$30,799/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>L | 271呎 (1房)
+$964万
+$35,587/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="M31" s="20" t="inlineStr">
+        <is>
+          <t>M | 279呎 (1房)
+$904万
+$32,400/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="N31" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-坚尼地城-Kennedy 38.xlsx
+++ b/files/港岛-坚尼地城-Kennedy 38.xlsx
@@ -670,7 +670,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-坚尼地城-Kennedy 38.xlsx
+++ b/files/港岛-坚尼地城-Kennedy 38.xlsx
@@ -2997,7 +2997,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>90 日付款計劃</t>
+          <t>90日付款計劃</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>90 日付款計劃</t>
+          <t>90日付款計劃</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>90 日付款計劃</t>
+          <t>90日付款計劃</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="M301" s="3" t="inlineStr">
         <is>
-          <t>90 日付款計劃</t>
+          <t>90日付款計劃</t>
         </is>
       </c>
       <c r="N301" s="3" t="inlineStr">

--- a/files/港岛-坚尼地城-Kennedy 38.xlsx
+++ b/files/港岛-坚尼地城-Kennedy 38.xlsx
@@ -2997,7 +2997,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -22189,22 +22189,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -22926,12 +22926,12 @@
 (21年-12月-13日)</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
 $965万
 $36,847/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -24591,12 +24591,12 @@
 (21年-12月-12日)</t>
         </is>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="F26" s="25" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
 $950万
 $36,248/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">

--- a/files/港岛-坚尼地城-Kennedy 38.xlsx
+++ b/files/港岛-坚尼地城-Kennedy 38.xlsx
@@ -22296,7 +22296,7 @@
           <t>A | 1000呎 (4+房)
 $4300万
 $43,000/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -22304,7 +22304,7 @@
           <t>B | 566呎 (2房)
 $2434万
 $43,000/呎
-(23年-06月-15日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -22312,7 +22312,7 @@
           <t>C | 796呎 (3房)
 $3224万
 $40,500/呎
-(23年-04月-25日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -22320,7 +22320,7 @@
           <t>D | 880呎 (3房)
 $3524万
 $40,045/呎
-(24年-05月-08日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr"/>
@@ -22352,7 +22352,7 @@
           <t>B | 287呎 (1房)
 $951万
 $33,136/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -22360,7 +22360,7 @@
           <t>C | 456呎 (2房)
 $1520万
 $33,341/呎
-(23年-04月-15日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -22368,7 +22368,7 @@
           <t>D | 332呎 (1房)
 $1035万
 $31,164/呎
-(23年-03月-29日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -22384,7 +22384,7 @@
           <t>F | 265呎 (开放式)
 $811万
 $30,617/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -22392,7 +22392,7 @@
           <t>G | 292呎 (1房)
 $902万
 $30,896/呎
-(23年-06月-25日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -22400,7 +22400,7 @@
           <t>H | 228呎 (开放式)
 $742万
 $32,526/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -22408,7 +22408,7 @@
           <t>J | 288呎 (1房)
 $890万
 $30,909/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -22416,7 +22416,7 @@
           <t>K | 298呎 (1房)
 $870万
 $29,208/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -22424,7 +22424,7 @@
           <t>L | 302呎 (1房)
 $973万
 $32,206/呎
-(21年-11月-25日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -22432,7 +22432,7 @@
           <t>M | 293呎 (1房)
 $963万
 $32,870/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -22440,7 +22440,7 @@
           <t>N | 300呎 (1房)
 $962万
 $32,074/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -22463,7 +22463,7 @@
           <t>B | 287呎 (1房)
 $946万
 $32,976/呎
-(21年-12月-30日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -22471,7 +22471,7 @@
           <t>C | 456呎 (2房)
 $1468万
 $32,200/呎
-(22年-05月-10日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -22479,7 +22479,7 @@
           <t>D | 332呎 (1房)
 $1030万
 $31,009/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -22495,7 +22495,7 @@
           <t>F | 265呎 (开放式)
 $806万
 $30,426/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -22503,7 +22503,7 @@
           <t>G | 292呎 (1房)
 $898万
 $30,742/呎
-(23年-06月-08日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -22511,7 +22511,7 @@
           <t>H | 228呎 (开放式)
 $740万
 $32,471/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -22519,7 +22519,7 @@
           <t>J | 288呎 (1房)
 $886万
 $30,759/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -22527,7 +22527,7 @@
           <t>K | 299呎 (1房)
 $885万
 $29,609/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -22535,7 +22535,7 @@
           <t>L | 302呎 (1房)
 $968万
 $32,057/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -22543,7 +22543,7 @@
           <t>M | 293呎 (1房)
 $958万
 $32,707/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -22551,7 +22551,7 @@
           <t>N | 301呎 (1房)
 $957万
 $31,809/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
           <t>B | 286呎 (1房)
 $921万
 $32,214/呎
-(23年-04月-12日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -22582,7 +22582,7 @@
           <t>C | 456呎 (2房)
 $1433万
 $31,421/呎
-(22年-02月-21日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -22590,7 +22590,7 @@
           <t>D | 333呎 (1房)
 $1047万
 $31,448/呎
-(22年-01月-27日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -22606,7 +22606,7 @@
           <t>F | 265呎 (开放式)
 $803万
 $30,315/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -22614,7 +22614,7 @@
           <t>G | 292呎 (1房)
 $893万
 $30,591/呎
-(23年-03月-27日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="I8" s="24" t="inlineStr">
@@ -22630,7 +22630,7 @@
           <t>J | 288呎 (1房)
 $882万
 $30,609/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -22638,7 +22638,7 @@
           <t>K | 298呎 (1房)
 $881万
 $29,560/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -22646,7 +22646,7 @@
           <t>L | 302呎 (1房)
 $964万
 $31,904/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -22654,7 +22654,7 @@
           <t>M | 293呎 (1房)
 $954万
 $32,544/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -22662,7 +22662,7 @@
           <t>N | 300呎 (1房)
 $932万
 $31,065/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
           <t>B | 286呎 (1房)
 $932万
 $32,594/呎
-(24年-06月-03日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -22693,7 +22693,7 @@
           <t>C | 456呎 (2房)
 $1408万
 $30,876/呎
-(22年-02月-03日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -22701,7 +22701,7 @@
           <t>D | 332呎 (1房)
 $1019万
 $30,703/呎
-(23年-04月-10日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -22717,7 +22717,7 @@
           <t>F | 265呎 (开放式)
 $799万
 $30,162/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -22725,7 +22725,7 @@
           <t>G | 292呎 (1房)
 $889万
 $30,437/呎
-(23年-04月-23日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -22733,7 +22733,7 @@
           <t>H | 228呎 (开放式)
 $733万
 $32,147/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -22741,7 +22741,7 @@
           <t>J | 288呎 (1房)
 $877万
 $30,462/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -22749,7 +22749,7 @@
           <t>K | 298呎 (1房)
 $877万
 $29,415/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -22757,7 +22757,7 @@
           <t>L | 302呎 (1房)
 $959万
 $31,755/呎
-(21年-12月-20日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -22765,7 +22765,7 @@
           <t>M | 293呎 (1房)
 $949万
 $32,382/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -22773,7 +22773,7 @@
           <t>N | 300呎 (1房)
 $948万
 $31,599/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -22796,7 +22796,7 @@
           <t>B | 287呎 (1房)
 $917万
 $31,948/呎
-(23年-07月-05日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -22804,7 +22804,7 @@
           <t>C | 456呎 (2房)
 $1357万
 $29,761/呎
-(21年-12月-30日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -22812,7 +22812,7 @@
           <t>D | 332呎 (1房)
 $1019万
 $30,703/呎
-(23年-04月-19日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -22820,7 +22820,7 @@
           <t>E | 262呎 (开放式)
 $876万
 $33,454/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -22828,7 +22828,7 @@
           <t>F | 264呎 (开放式)
 $817万
 $30,949/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -22836,7 +22836,7 @@
           <t>G | 292呎 (1房)
 $889万
 $30,437/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -22844,7 +22844,7 @@
           <t>H | 228呎 (开放式)
 $770万
 $33,758/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -22852,7 +22852,7 @@
           <t>J | 288呎 (1房)
 $877万
 $30,462/呎
-(21年-12月-28日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -22860,7 +22860,7 @@
           <t>K | 298呎 (1房)
 $877万
 $29,415/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -22868,7 +22868,7 @@
           <t>L | 302呎 (1房)
 $959万
 $31,755/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -22876,7 +22876,7 @@
           <t>M | 293呎 (1房)
 $949万
 $32,382/呎
-(25年-07月-27日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -22884,7 +22884,7 @@
           <t>N | 301呎 (1房)
 $948万
 $31,494/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -22907,7 +22907,7 @@
           <t>B | 286呎 (1房)
 $907万
 $31,717/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -22915,7 +22915,7 @@
           <t>C | 456呎 (2房)
 $1339万
 $29,366/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -22923,7 +22923,7 @@
           <t>D | 333呎 (1房)
 $1011万
 $30,370/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
@@ -22939,7 +22939,7 @@
           <t>F | 265呎 (开放式)
 $791万
 $29,843/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -22947,7 +22947,7 @@
           <t>G | 292呎 (1房)
 $880万
 $30,135/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I11" s="24" t="inlineStr">
@@ -22963,7 +22963,7 @@
           <t>J | 288呎 (1房)
 $869万
 $30,168/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -22971,7 +22971,7 @@
           <t>K | 299呎 (1房)
 $852万
 $28,511/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -22979,7 +22979,7 @@
           <t>L | 302呎 (1房)
 $934万
 $30,924/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -22987,7 +22987,7 @@
           <t>M | 293呎 (1房)
 $939万
 $32,059/呎
-(25年-07月-27日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -22995,7 +22995,7 @@
           <t>N | 300呎 (1房)
 $938万
 $31,283/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -23018,7 +23018,7 @@
           <t>B | 286呎 (1房)
 $903万
 $31,563/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -23026,7 +23026,7 @@
           <t>C | 456呎 (2房)
 $1365万
 $29,928/呎
-(21年-12月-20日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -23034,7 +23034,7 @@
           <t>D | 332呎 (1房)
 $1019万
 $30,679/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -23050,7 +23050,7 @@
           <t>F | 265呎 (开放式)
 $804万
 $30,353/呎
-(22年-03月-08日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -23058,7 +23058,7 @@
           <t>G | 292呎 (1房)
 $875万
 $29,965/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -23066,7 +23066,7 @@
           <t>H | 228呎 (开放式)
 $726万
 $31,839/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -23074,7 +23074,7 @@
           <t>J | 288呎 (1房)
 $841万
 $29,203/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -23082,7 +23082,7 @@
           <t>K | 298呎 (1房)
 $830万
 $27,846/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -23090,7 +23090,7 @@
           <t>L | 302呎 (1房)
 $909万
 $30,108/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -23098,7 +23098,7 @@
           <t>M | 293呎 (1房)
 $935万
 $31,899/呎
-(23年-12月-14日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -23106,7 +23106,7 @@
           <t>N | 300呎 (1房)
 $934万
 $31,130/呎
-(21年-12月-20日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
           <t>B | 287呎 (1房)
 $898万
 $31,302/呎
-(23年-05月-08日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -23137,7 +23137,7 @@
           <t>C | 456呎 (2房)
 $1391万
 $30,511/呎
-(22年-02月-13日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -23145,7 +23145,7 @@
           <t>D | 332呎 (1房)
 $1013万
 $30,526/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -23153,7 +23153,7 @@
           <t>E | 262呎 (开放式)
 $779万
 $29,717/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -23161,7 +23161,7 @@
           <t>F | 265呎 (开放式)
 $796万
 $30,054/呎
-(21年-11月-19日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -23169,7 +23169,7 @@
           <t>G | 292呎 (1房)
 $866万
 $29,641/呎
-(23年-05月-18日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -23177,7 +23177,7 @@
           <t>H | 228呎 (开放式)
 $711万
 $31,164/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -23185,7 +23185,7 @@
           <t>J | 288呎 (1房)
 $819万
 $28,428/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -23193,7 +23193,7 @@
           <t>K | 298呎 (1房)
 $826万
 $27,710/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -23201,7 +23201,7 @@
           <t>L | 302呎 (1房)
 $925万
 $30,634/呎
-(21年-12月-20日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -23209,7 +23209,7 @@
           <t>M | 292呎 (1房)
 $941万
 $32,219/呎
-(23年-05月-08日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -23217,7 +23217,7 @@
           <t>N | 301呎 (1房)
 $929万
 $30,870/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -23240,7 +23240,7 @@
           <t>B | 287呎 (1房)
 $894万
 $31,149/呎
-(23年-06月-06日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -23248,7 +23248,7 @@
           <t>C | 456呎 (2房)
 $1367万
 $29,975/呎
-(22年-01月-16日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -23256,7 +23256,7 @@
           <t>D | 332呎 (1房)
 $1008万
 $30,374/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -23264,7 +23264,7 @@
           <t>E | 262呎 (开放式)
 $775万
 $29,569/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -23272,7 +23272,7 @@
           <t>F | 265呎 (开放式)
 $792万
 $29,905/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -23280,7 +23280,7 @@
           <t>G | 292呎 (1房)
 $861万
 $29,497/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -23288,7 +23288,7 @@
           <t>H | 228呎 (开放式)
 $687万
 $30,146/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -23296,7 +23296,7 @@
           <t>J | 288呎 (1房)
 $833万
 $28,916/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -23304,7 +23304,7 @@
           <t>K | 298呎 (1房)
 $840万
 $28,183/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -23312,7 +23312,7 @@
           <t>L | 302呎 (1房)
 $921万
 $30,488/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -23320,7 +23320,7 @@
           <t>M | 293呎 (1房)
 $916万
 $31,254/呎
-(25年-07月-24日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23328,7 +23328,7 @@
           <t>N | 301呎 (1房)
 $925万
 $30,718/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -23351,7 +23351,7 @@
           <t>B | 287呎 (1房)
 $885万
 $30,826/呎
-(22年-04月-19日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -23359,7 +23359,7 @@
           <t>C | 456呎 (2房)
 $1323万
 $29,015/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -23367,7 +23367,7 @@
           <t>D | 332呎 (1房)
 $992万
 $29,865/呎
-(21年-12月-22日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -23375,7 +23375,7 @@
           <t>E | 262呎 (开放式)
 $771万
 $29,422/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -23383,7 +23383,7 @@
           <t>F | 264呎 (开放式)
 $771万
 $29,219/呎
-(21年-12月-22日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -23391,7 +23391,7 @@
           <t>G | 292呎 (1房)
 $857万
 $29,349/呎
-(22年-06月-08日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -23399,7 +23399,7 @@
           <t>H | 228呎 (开放式)
 $684万
 $29,996/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -23407,7 +23407,7 @@
           <t>J | 288呎 (1房)
 $829万
 $28,769/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -23415,7 +23415,7 @@
           <t>K | 299呎 (1房)
 $836万
 $27,947/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -23423,7 +23423,7 @@
           <t>L | 302呎 (1房)
 $867万
 $28,721/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -23431,7 +23431,7 @@
           <t>M | 293呎 (1房)
 $888万
 $30,311/呎
-(24年-02月-28日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23439,7 +23439,7 @@
           <t>N | 300呎 (1房)
 $907万
 $30,231/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -23462,7 +23462,7 @@
           <t>B | 287呎 (1房)
 $883万
 $30,767/呎
-(21年-12月-30日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -23470,7 +23470,7 @@
           <t>C | 456呎 (2房)
 $1294万
 $28,370/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -23478,7 +23478,7 @@
           <t>D | 332呎 (1房)
 $989万
 $29,797/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -23486,7 +23486,7 @@
           <t>E | 262呎 (开放式)
 $767万
 $29,277/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -23494,7 +23494,7 @@
           <t>F | 265呎 (开放式)
 $785万
 $29,610/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -23502,7 +23502,7 @@
           <t>G | 292呎 (1房)
 $872万
 $29,853/呎
-(22年-06月-07日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -23510,7 +23510,7 @@
           <t>H | 228呎 (开放式)
 $680万
 $29,846/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -23518,7 +23518,7 @@
           <t>J | 288呎 (1房)
 $824万
 $28,628/呎
-(21年-12月-21日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -23526,7 +23526,7 @@
           <t>K | 298呎 (1房)
 $831万
 $27,902/呎
-(21年-12月-21日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -23534,7 +23534,7 @@
           <t>L | 302呎 (1房)
 $846万
 $28,017/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -23542,7 +23542,7 @@
           <t>M | 293呎 (1房)
 $870万
 $29,706/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -23550,7 +23550,7 @@
           <t>N | 301呎 (1房)
 $894万
 $29,690/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -23573,7 +23573,7 @@
           <t>B | 287呎 (1房)
 $879万
 $30,616/呎
-(22年-01月-05日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -23581,7 +23581,7 @@
           <t>C | 456呎 (2房)
 $1290万
 $28,285/呎
-(22年-01月-03日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -23589,7 +23589,7 @@
           <t>D | 332呎 (1房)
 $953万
 $28,705/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -23597,7 +23597,7 @@
           <t>E | 262呎 (开放式)
 $801万
 $30,586/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -23605,7 +23605,7 @@
           <t>F | 264呎 (开放式)
 $764万
 $28,930/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -23613,7 +23613,7 @@
           <t>G | 292呎 (1房)
 $863万
 $29,540/呎
-(23年-12月-13日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -23621,7 +23621,7 @@
           <t>H | 228呎 (开放式)
 $677万
 $29,700/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -23629,7 +23629,7 @@
           <t>J | 288呎 (1房)
 $802万
 $27,847/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -23637,7 +23637,7 @@
           <t>K | 298呎 (1房)
 $809万
 $27,142/呎
-(21年-11月-19日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -23645,7 +23645,7 @@
           <t>L | 302呎 (1房)
 $842万
 $27,877/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -23653,7 +23653,7 @@
           <t>M | 293呎 (1房)
 $866万
 $29,559/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -23661,7 +23661,7 @@
           <t>N | 301呎 (1房)
 $870万
 $28,902/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -23684,7 +23684,7 @@
           <t>B | 287呎 (1房)
 $874万
 $30,469/呎
-(21年-11月-27日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -23692,7 +23692,7 @@
           <t>C | 456呎 (2房)
 $1354万
 $29,692/呎
-(22年-05月-24日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -23700,7 +23700,7 @@
           <t>D | 332呎 (1房)
 $969万
 $29,199/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -23708,7 +23708,7 @@
           <t>E | 262呎 (开放式)
 $797万
 $30,435/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -23716,7 +23716,7 @@
           <t>F | 264呎 (开放式)
 $777万
 $29,426/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -23724,7 +23724,7 @@
           <t>G | 292呎 (1房)
 $844万
 $28,911/呎
-(23年-08月-21日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -23732,7 +23732,7 @@
           <t>H | 228呎 (开放式)
 $674万
 $29,550/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -23740,7 +23740,7 @@
           <t>J | 288呎 (1房)
 $816万
 $28,325/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -23748,7 +23748,7 @@
           <t>K | 299呎 (1房)
 $823万
 $27,517/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -23756,7 +23756,7 @@
           <t>L | 302呎 (1房)
 $820万
 $27,137/呎
-(21年-11月-19日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -23764,7 +23764,7 @@
           <t>M | 293呎 (1房)
 $862万
 $29,411/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -23772,7 +23772,7 @@
           <t>N | 300呎 (1房)
 $885万
 $29,495/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -23795,7 +23795,7 @@
           <t>B | 287呎 (1房)
 $855万
 $29,807/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -23803,7 +23803,7 @@
           <t>C | 456呎 (2房)
 $1354万
 $29,692/呎
-(22年-08月-16日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -23811,7 +23811,7 @@
           <t>D | 332呎 (1房)
 $969万
 $29,199/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -23819,7 +23819,7 @@
           <t>E | 262呎 (开放式)
 $797万
 $30,435/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -23827,7 +23827,7 @@
           <t>F | 264呎 (开放式)
 $777万
 $29,426/呎
-(21年-12月-19日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -23835,7 +23835,7 @@
           <t>G | 292呎 (1房)
 $844万
 $28,911/呎
-(25年-07月-27日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -23843,7 +23843,7 @@
           <t>H | 228呎 (开放式)
 $694万
 $30,438/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -23851,7 +23851,7 @@
           <t>J | 288呎 (1房)
 $816万
 $28,325/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -23859,7 +23859,7 @@
           <t>K | 298呎 (1房)
 $823万
 $27,609/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -23867,7 +23867,7 @@
           <t>L | 302呎 (1房)
 $838万
 $27,740/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -23875,7 +23875,7 @@
           <t>M | 293呎 (1房)
 $862万
 $29,411/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -23883,7 +23883,7 @@
           <t>N | 301呎 (1房)
 $885万
 $29,397/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -23906,7 +23906,7 @@
           <t>B | 286呎 (1房)
 $844万
 $29,523/呎
-(21年-12月-21日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -23914,7 +23914,7 @@
           <t>C | 456呎 (2房)
 $1313万
 $28,788/呎
-(23年-02月-21日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -23922,7 +23922,7 @@
           <t>D | 332呎 (1房)
 $965万
 $29,071/呎
-(21年-12月-21日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -23930,7 +23930,7 @@
           <t>E | 262呎 (开放式)
 $786万
 $29,992/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -23938,7 +23938,7 @@
           <t>F | 264呎 (开放式)
 $746万
 $28,264/呎
-(23年-04月-12日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -23946,7 +23946,7 @@
           <t>G | 292呎 (1房)
 $816万
 $27,949/呎
-(22年-08月-16日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -23954,7 +23954,7 @@
           <t>H | 228呎 (开放式)
 $664万
 $29,112/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -23962,7 +23962,7 @@
           <t>J | 288呎 (1房)
 $789万
 $27,408/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -23970,7 +23970,7 @@
           <t>K | 299呎 (1房)
 $810万
 $27,104/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -23978,7 +23978,7 @@
           <t>L | 302呎 (1房)
 $825万
 $27,326/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -23986,7 +23986,7 @@
           <t>M | 293呎 (1房)
 $824万
 $28,115/呎
-(24年-06月-10日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -23994,7 +23994,7 @@
           <t>N | 301呎 (1房)
 $855万
 $28,398/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
           <t>B | 287呎 (1房)
 $822万
 $28,637/呎
-(21年-12月-20日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -24025,7 +24025,7 @@
           <t>C | 456呎 (2房)
 $1309万
 $28,703/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -24033,7 +24033,7 @@
           <t>D | 332呎 (1房)
 $950万
 $28,620/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -24041,7 +24041,7 @@
           <t>E | 262呎 (开放式)
 $730万
 $27,859/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -24049,7 +24049,7 @@
           <t>F | 265呎 (开放式)
 $730万
 $27,557/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -24057,7 +24057,7 @@
           <t>G | 292呎 (1房)
 $812万
 $27,811/呎
-(23年-04月-27日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -24065,7 +24065,7 @@
           <t>H | 228呎 (开放式)
 $646万
 $28,354/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -24073,7 +24073,7 @@
           <t>J | 288呎 (1房)
 $785万
 $27,271/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -24081,7 +24081,7 @@
           <t>K | 299呎 (1房)
 $806万
 $26,969/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -24089,7 +24089,7 @@
           <t>L | 302呎 (1房)
 $821万
 $27,189/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -24097,7 +24097,7 @@
           <t>M | 293呎 (1房)
 $835万
 $28,499/呎
-(24年-02月-18日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -24105,7 +24105,7 @@
           <t>N | 300呎 (1房)
 $850万
 $28,348/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -24128,7 +24128,7 @@
           <t>B | 287呎 (1房)
 $818万
 $28,493/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -24136,7 +24136,7 @@
           <t>C | 456呎 (2房)
 $1295万
 $28,399/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -24144,7 +24144,7 @@
           <t>D | 332呎 (1房)
 $945万
 $28,476/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -24152,7 +24152,7 @@
           <t>E | 262呎 (开放式)
 $789万
 $30,116/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -24160,7 +24160,7 @@
           <t>F | 265呎 (开放式)
 $743万
 $28,030/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -24168,7 +24168,7 @@
           <t>G | 292呎 (1房)
 $808万
 $27,672/呎
-(23年-03月-21日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -24176,7 +24176,7 @@
           <t>H | 228呎 (开放式)
 $644万
 $28,255/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -24184,7 +24184,7 @@
           <t>J | 288呎 (1房)
 $781万
 $27,133/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -24192,7 +24192,7 @@
           <t>K | 298呎 (1房)
 $802万
 $26,924/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -24200,7 +24200,7 @@
           <t>L | 302呎 (1房)
 $799万
 $26,467/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -24208,7 +24208,7 @@
           <t>M | 293呎 (1房)
 $819万
 $27,949/呎
-(23年-05月-29日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -24216,7 +24216,7 @@
           <t>N | 301呎 (1房)
 $846万
 $28,113/呎
-(21年-12月-19日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -24239,7 +24239,7 @@
           <t>B | 286呎 (1房)
 $832万
 $29,083/呎
-(21年-12月-19日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -24247,7 +24247,7 @@
           <t>C | 456呎 (2房)
 $1291万
 $28,312/呎
-(22年-01月-10日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -24255,7 +24255,7 @@
           <t>D | 333呎 (1房)
 $951万
 $28,556/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -24263,7 +24263,7 @@
           <t>E | 262呎 (开放式)
 $723万
 $27,581/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -24271,7 +24271,7 @@
           <t>F | 265呎 (开放式)
 $739万
 $27,888/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -24279,7 +24279,7 @@
           <t>G | 292呎 (1房)
 $804万
 $27,533/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -24287,7 +24287,7 @@
           <t>H | 228呎 (开放式)
 $640万
 $28,069/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -24295,7 +24295,7 @@
           <t>J | 288呎 (1房)
 $778万
 $26,999/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -24303,7 +24303,7 @@
           <t>K | 298呎 (1房)
 $798万
 $26,791/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -24311,7 +24311,7 @@
           <t>L | 302呎 (1房)
 $813万
 $26,918/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
@@ -24319,7 +24319,7 @@
           <t>M | 293呎 (1房)
 $819万
 $27,940/呎
-(25年-08月-05日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -24327,7 +24327,7 @@
           <t>N | 301呎 (1房)
 $842万
 $27,973/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -24350,7 +24350,7 @@
           <t>B | 287呎 (1房)
 $828万
 $28,837/呎
-(21年-12月-20日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -24358,7 +24358,7 @@
           <t>C | 456呎 (2房)
 $1287万
 $28,227/呎
-(22年-01月-11日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -24366,7 +24366,7 @@
           <t>D | 333呎 (1房)
 $916万
 $27,497/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -24374,7 +24374,7 @@
           <t>E | 262呎 (开放式)
 $735万
 $28,053/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -24382,7 +24382,7 @@
           <t>F | 265呎 (开放式)
 $719万
 $27,146/呎
-(21年-11月-19日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -24390,7 +24390,7 @@
           <t>G | 292呎 (1房)
 $800万
 $27,395/呎
-(23年-06月-18日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -24398,7 +24398,7 @@
           <t>H | 228呎 (开放式)
 $652万
 $28,596/呎
-(22年-01月-11日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -24406,7 +24406,7 @@
           <t>J | 288呎 (1房)
 $774万
 $26,865/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -24414,7 +24414,7 @@
           <t>K | 298呎 (1房)
 $794万
 $26,655/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -24422,7 +24422,7 @@
           <t>L | 302呎 (1房)
 $809万
 $26,783/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -24430,7 +24430,7 @@
           <t>M | 292呎 (1房)
 $814万
 $27,875/呎
-(23年-09月-04日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -24438,7 +24438,7 @@
           <t>N | 300呎 (1房)
 $838万
 $27,925/呎
-(21年-12月-19日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
           <t>B | 286呎 (1房)
 $815万
 $28,510/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -24469,7 +24469,7 @@
           <t>C | 456呎 (2房)
 $1287万
 $28,220/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -24477,7 +24477,7 @@
           <t>D | 333呎 (1房)
 $927万
 $27,829/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -24485,7 +24485,7 @@
           <t>E | 262呎 (开放式)
 $715万
 $27,306/呎
-(26年-01月-27日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -24493,7 +24493,7 @@
           <t>F | 264呎 (开放式)
 $732万
 $27,715/呎
-(21年-12月-07日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -24501,7 +24501,7 @@
           <t>G | 292呎 (1房)
 $796万
 $27,259/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -24509,7 +24509,7 @@
           <t>H | 229呎 (开放式)
 $649万
 $28,327/呎
-(21年-12月-19日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -24517,7 +24517,7 @@
           <t>J | 288呎 (1房)
 $770万
 $26,728/呎
-(21年-12月-07日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -24525,7 +24525,7 @@
           <t>K | 299呎 (1房)
 $790万
 $26,434/呎
-(21年-12月-07日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -24533,7 +24533,7 @@
           <t>L | 302呎 (1房)
 $805万
 $26,649/呎
-(21年-12月-07日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -24541,7 +24541,7 @@
           <t>M | 293呎 (1房)
 $804万
 $27,424/呎
-(24年-07月-07日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -24549,7 +24549,7 @@
           <t>N | 300呎 (1房)
 $825万
 $27,511/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -24572,7 +24572,7 @@
           <t>B | 286呎 (1房)
 $815万
 $28,510/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -24580,7 +24580,7 @@
           <t>C | 456呎 (2房)
 $1287万
 $28,220/呎
-(23年-03月-19日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -24588,7 +24588,7 @@
           <t>D | 332呎 (1房)
 $927万
 $27,913/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr">
@@ -24604,7 +24604,7 @@
           <t>F | 264呎 (开放式)
 $732万
 $27,715/呎
-(21年-12月-07日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -24612,7 +24612,7 @@
           <t>G | 292呎 (1房)
 $752万
 $25,761/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -24620,7 +24620,7 @@
           <t>H | 228呎 (开放式)
 $649万
 $28,451/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -24628,7 +24628,7 @@
           <t>J | 288呎 (1房)
 $770万
 $26,728/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -24636,7 +24636,7 @@
           <t>K | 298呎 (1房)
 $790万
 $26,522/呎
-(21年-12月-07日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -24644,7 +24644,7 @@
           <t>L | 302呎 (1房)
 $805万
 $26,649/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr">
@@ -24652,7 +24652,7 @@
           <t>M | 293呎 (1房)
 $804万
 $27,424/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -24660,7 +24660,7 @@
           <t>N | 301呎 (1房)
 $825万
 $27,420/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -24683,7 +24683,7 @@
           <t>B | 286呎 (1房)
 $807万
 $28,227/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -24691,7 +24691,7 @@
           <t>C | 456呎 (2房)
 $1311万
 $28,747/呎
-(23年-04月-11日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -24699,7 +24699,7 @@
           <t>D | 333呎 (1房)
 $908万
 $27,254/呎
-(24年-12月-22日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -24707,7 +24707,7 @@
           <t>E | 262呎 (开放式)
 $701万
 $26,766/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -24715,7 +24715,7 @@
           <t>F | 265呎 (开放式)
 $724万
 $27,336/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -24723,7 +24723,7 @@
           <t>G | 292呎 (1房)
 $761万
 $26,072/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -24731,7 +24731,7 @@
           <t>H | 229呎 (开放式)
 $628万
 $27,436/呎
-(23年-05月-09日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -24739,7 +24739,7 @@
           <t>J | 288呎 (1房)
 $762万
 $26,462/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
@@ -24747,7 +24747,7 @@
           <t>K | 298呎 (1房)
 $782万
 $26,257/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -24755,7 +24755,7 @@
           <t>L | 302呎 (1房)
 $797万
 $26,384/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
@@ -24763,7 +24763,7 @@
           <t>M | 293呎 (1房)
 $799万
 $27,258/呎
-(24年-05月-08日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24771,7 +24771,7 @@
           <t>N | 301呎 (1房)
 $817万
 $27,148/呎
-(21年-12月-28日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -24794,7 +24794,7 @@
           <t>B | 286呎 (1房)
 $804万
 $28,118/呎
-(21年-12月-22日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -24802,7 +24802,7 @@
           <t>C | 456呎 (2房)
 $1265万
 $27,739/呎
-(23年-03月-16日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -24810,7 +24810,7 @@
           <t>D | 332呎 (1房)
 $914万
 $27,533/呎
-(22年-01月-12日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F28" s="25" t="inlineStr">
@@ -24826,7 +24826,7 @@
           <t>F | 264呎 (开放式)
 $721万
 $27,300/呎
-(22年-04月-28日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -24834,7 +24834,7 @@
           <t>G | 292呎 (1房)
 $758万
 $25,942/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -24842,7 +24842,7 @@
           <t>H | 229呎 (开放式)
 $638万
 $27,881/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -24850,7 +24850,7 @@
           <t>J | 288呎 (1房)
 $742万
 $25,759/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K28" s="20" t="inlineStr">
@@ -24858,7 +24858,7 @@
           <t>K | 299呎 (1房)
 $762万
 $25,474/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -24866,7 +24866,7 @@
           <t>L | 302呎 (1房)
 $793万
 $26,253/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M28" s="20" t="inlineStr">
@@ -24874,7 +24874,7 @@
           <t>M | 293呎 (1房)
 $810万
 $27,631/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -24882,7 +24882,7 @@
           <t>N | 300呎 (1房)
 $813万
 $27,100/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -24905,7 +24905,7 @@
           <t>B | 287呎 (1房)
 $781万
 $27,226/呎
-(21年-12月-21日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -24913,7 +24913,7 @@
           <t>C | 456呎 (2房)
 $1248万
 $27,368/呎
-(22年-01月-16日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -24921,7 +24921,7 @@
           <t>D | 333呎 (1房)
 $898万
 $26,981/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -24929,7 +24929,7 @@
           <t>E | 262呎 (开放式)
 $709万
 $27,063/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -24937,7 +24937,7 @@
           <t>F | 265呎 (开放式)
 $701万
 $26,446/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -24945,7 +24945,7 @@
           <t>G | 292呎 (1房)
 $753万
 $25,785/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -24953,7 +24953,7 @@
           <t>H | 228呎 (开放式)
 $635万
 $27,834/呎
-(22年-09月-19日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -24961,7 +24961,7 @@
           <t>J | 288呎 (1房)
 $754万
 $26,172/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -24969,7 +24969,7 @@
           <t>K | 299呎 (1房)
 $757万
 $25,320/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L29" s="20" t="inlineStr">
@@ -24977,7 +24977,7 @@
           <t>L | 302呎 (1房)
 $788万
 $26,095/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr">
@@ -24985,7 +24985,7 @@
           <t>M | 293呎 (1房)
 $794万
 $27,095/呎
-(25年-09月-04日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24993,7 +24993,7 @@
           <t>N | 300呎 (1房)
 $809万
 $26,965/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
           <t>B | 286呎 (1房)
 $778万
 $27,217/呎
-(22年-01月-12日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -25024,7 +25024,7 @@
           <t>C | 456呎 (2房)
 $1248万
 $27,365/呎
-(23年-06月-18日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -25032,7 +25032,7 @@
           <t>D | 333呎 (1房)
 $894万
 $26,846/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -25040,7 +25040,7 @@
           <t>E | 262呎 (开放式)
 $690万
 $26,340/呎
-(23年-08月-10日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -25048,7 +25048,7 @@
           <t>F | 265呎 (开放式)
 $697万
 $26,314/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -25056,7 +25056,7 @@
           <t>G | 292呎 (1房)
 $750万
 $25,675/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -25064,7 +25064,7 @@
           <t>H | 229呎 (开放式)
 $632万
 $27,600/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -25072,7 +25072,7 @@
           <t>J | 288呎 (1房)
 $750万
 $26,041/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K30" s="20" t="inlineStr">
@@ -25080,7 +25080,7 @@
           <t>K | 298呎 (1房)
 $770万
 $25,840/呎
-(21年-12月-21日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L30" s="20" t="inlineStr">
@@ -25088,7 +25088,7 @@
           <t>L | 302呎 (1房)
 $784万
 $25,964/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="M30" s="20" t="inlineStr">
@@ -25096,7 +25096,7 @@
           <t>M | 293呎 (1房)
 $792万
 $27,015/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
@@ -25104,7 +25104,7 @@
           <t>N | 300呎 (1房)
 $805万
 $26,830/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
           <t>C | 309呎 (1房)
 $947万
 $30,638/呎
-(23年-03月-02日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -25143,7 +25143,7 @@
           <t>D | 240呎 (开放式)
 $756万
 $31,502/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -25151,7 +25151,7 @@
           <t>E | 243呎 (开放式)
 $804万
 $33,100/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -25159,7 +25159,7 @@
           <t>F | 270呎 (1房)
 $814万
 $30,130/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -25167,7 +25167,7 @@
           <t>G | 207呎 (开放式)
 $637万
 $30,765/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -25175,7 +25175,7 @@
           <t>H | 267呎 (1房)
 $763万
 $28,561/呎
-(21年-12月-07日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -25183,7 +25183,7 @@
           <t>J | 278呎 (1房)
 $802万
 $28,861/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -25191,7 +25191,7 @@
           <t>K | 279呎 (1房)
 $859万
 $30,799/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="L31" s="20" t="inlineStr">
@@ -25199,7 +25199,7 @@
           <t>L | 271呎 (1房)
 $964万
 $35,587/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="M31" s="20" t="inlineStr">
@@ -25207,7 +25207,7 @@
           <t>M | 279呎 (1房)
 $904万
 $32,400/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr"/>

--- a/files/港岛-坚尼地城-Kennedy 38.xlsx
+++ b/files/港岛-坚尼地城-Kennedy 38.xlsx
@@ -22296,7 +22296,7 @@
           <t>A | 1000呎 (4+房)
 $4300万
 $43,000/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -22304,7 +22304,7 @@
           <t>B | 566呎 (2房)
 $2434万
 $43,000/呎
-(23年-06月)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -22312,7 +22312,7 @@
           <t>C | 796呎 (3房)
 $3224万
 $40,500/呎
-(23年-04月)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -22320,7 +22320,7 @@
           <t>D | 880呎 (3房)
 $3524万
 $40,045/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr"/>
@@ -22352,7 +22352,7 @@
           <t>B | 287呎 (1房)
 $951万
 $33,136/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -22360,7 +22360,7 @@
           <t>C | 456呎 (2房)
 $1520万
 $33,341/呎
-(23年-04月)</t>
+(23年-04月-15日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -22368,7 +22368,7 @@
           <t>D | 332呎 (1房)
 $1035万
 $31,164/呎
-(23年-03月)</t>
+(23年-03月-29日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -22384,7 +22384,7 @@
           <t>F | 265呎 (开放式)
 $811万
 $30,617/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -22392,7 +22392,7 @@
           <t>G | 292呎 (1房)
 $902万
 $30,896/呎
-(23年-06月)</t>
+(23年-06月-25日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -22400,7 +22400,7 @@
           <t>H | 228呎 (开放式)
 $742万
 $32,526/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -22408,7 +22408,7 @@
           <t>J | 288呎 (1房)
 $890万
 $30,909/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -22416,7 +22416,7 @@
           <t>K | 298呎 (1房)
 $870万
 $29,208/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -22424,7 +22424,7 @@
           <t>L | 302呎 (1房)
 $973万
 $32,206/呎
-(21年-11月)</t>
+(21年-11月-25日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -22432,7 +22432,7 @@
           <t>M | 293呎 (1房)
 $963万
 $32,870/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -22440,7 +22440,7 @@
           <t>N | 300呎 (1房)
 $962万
 $32,074/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -22463,7 +22463,7 @@
           <t>B | 287呎 (1房)
 $946万
 $32,976/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -22471,7 +22471,7 @@
           <t>C | 456呎 (2房)
 $1468万
 $32,200/呎
-(22年-05月)</t>
+(22年-05月-10日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -22479,7 +22479,7 @@
           <t>D | 332呎 (1房)
 $1030万
 $31,009/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -22495,7 +22495,7 @@
           <t>F | 265呎 (开放式)
 $806万
 $30,426/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -22503,7 +22503,7 @@
           <t>G | 292呎 (1房)
 $898万
 $30,742/呎
-(23年-06月)</t>
+(23年-06月-08日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -22511,7 +22511,7 @@
           <t>H | 228呎 (开放式)
 $740万
 $32,471/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -22519,7 +22519,7 @@
           <t>J | 288呎 (1房)
 $886万
 $30,759/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -22527,7 +22527,7 @@
           <t>K | 299呎 (1房)
 $885万
 $29,609/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -22535,7 +22535,7 @@
           <t>L | 302呎 (1房)
 $968万
 $32,057/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -22543,7 +22543,7 @@
           <t>M | 293呎 (1房)
 $958万
 $32,707/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -22551,7 +22551,7 @@
           <t>N | 301呎 (1房)
 $957万
 $31,809/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
           <t>B | 286呎 (1房)
 $921万
 $32,214/呎
-(23年-04月)</t>
+(23年-04月-12日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -22582,7 +22582,7 @@
           <t>C | 456呎 (2房)
 $1433万
 $31,421/呎
-(22年-02月)</t>
+(22年-02月-21日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -22590,7 +22590,7 @@
           <t>D | 333呎 (1房)
 $1047万
 $31,448/呎
-(22年-01月)</t>
+(22年-01月-27日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -22606,7 +22606,7 @@
           <t>F | 265呎 (开放式)
 $803万
 $30,315/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -22614,7 +22614,7 @@
           <t>G | 292呎 (1房)
 $893万
 $30,591/呎
-(23年-03月)</t>
+(23年-03月-27日)</t>
         </is>
       </c>
       <c r="I8" s="24" t="inlineStr">
@@ -22630,7 +22630,7 @@
           <t>J | 288呎 (1房)
 $882万
 $30,609/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -22638,7 +22638,7 @@
           <t>K | 298呎 (1房)
 $881万
 $29,560/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -22646,7 +22646,7 @@
           <t>L | 302呎 (1房)
 $964万
 $31,904/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -22654,7 +22654,7 @@
           <t>M | 293呎 (1房)
 $954万
 $32,544/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -22662,7 +22662,7 @@
           <t>N | 300呎 (1房)
 $932万
 $31,065/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
           <t>B | 286呎 (1房)
 $932万
 $32,594/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -22693,7 +22693,7 @@
           <t>C | 456呎 (2房)
 $1408万
 $30,876/呎
-(22年-02月)</t>
+(22年-02月-03日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -22701,7 +22701,7 @@
           <t>D | 332呎 (1房)
 $1019万
 $30,703/呎
-(23年-04月)</t>
+(23年-04月-10日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -22717,7 +22717,7 @@
           <t>F | 265呎 (开放式)
 $799万
 $30,162/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -22725,7 +22725,7 @@
           <t>G | 292呎 (1房)
 $889万
 $30,437/呎
-(23年-04月)</t>
+(23年-04月-23日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -22733,7 +22733,7 @@
           <t>H | 228呎 (开放式)
 $733万
 $32,147/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -22741,7 +22741,7 @@
           <t>J | 288呎 (1房)
 $877万
 $30,462/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -22749,7 +22749,7 @@
           <t>K | 298呎 (1房)
 $877万
 $29,415/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -22757,7 +22757,7 @@
           <t>L | 302呎 (1房)
 $959万
 $31,755/呎
-(21年-12月)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -22765,7 +22765,7 @@
           <t>M | 293呎 (1房)
 $949万
 $32,382/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -22773,7 +22773,7 @@
           <t>N | 300呎 (1房)
 $948万
 $31,599/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -22796,7 +22796,7 @@
           <t>B | 287呎 (1房)
 $917万
 $31,948/呎
-(23年-07月)</t>
+(23年-07月-05日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -22804,7 +22804,7 @@
           <t>C | 456呎 (2房)
 $1357万
 $29,761/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -22812,7 +22812,7 @@
           <t>D | 332呎 (1房)
 $1019万
 $30,703/呎
-(23年-04月)</t>
+(23年-04月-19日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -22820,7 +22820,7 @@
           <t>E | 262呎 (开放式)
 $876万
 $33,454/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -22828,7 +22828,7 @@
           <t>F | 264呎 (开放式)
 $817万
 $30,949/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -22836,7 +22836,7 @@
           <t>G | 292呎 (1房)
 $889万
 $30,437/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -22844,7 +22844,7 @@
           <t>H | 228呎 (开放式)
 $770万
 $33,758/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -22852,7 +22852,7 @@
           <t>J | 288呎 (1房)
 $877万
 $30,462/呎
-(21年-12月)</t>
+(21年-12月-28日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -22860,7 +22860,7 @@
           <t>K | 298呎 (1房)
 $877万
 $29,415/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -22868,7 +22868,7 @@
           <t>L | 302呎 (1房)
 $959万
 $31,755/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -22876,7 +22876,7 @@
           <t>M | 293呎 (1房)
 $949万
 $32,382/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -22884,7 +22884,7 @@
           <t>N | 301呎 (1房)
 $948万
 $31,494/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -22907,7 +22907,7 @@
           <t>B | 286呎 (1房)
 $907万
 $31,717/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -22915,7 +22915,7 @@
           <t>C | 456呎 (2房)
 $1339万
 $29,366/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -22923,7 +22923,7 @@
           <t>D | 333呎 (1房)
 $1011万
 $30,370/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
@@ -22939,7 +22939,7 @@
           <t>F | 265呎 (开放式)
 $791万
 $29,843/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -22947,7 +22947,7 @@
           <t>G | 292呎 (1房)
 $880万
 $30,135/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I11" s="24" t="inlineStr">
@@ -22963,7 +22963,7 @@
           <t>J | 288呎 (1房)
 $869万
 $30,168/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -22971,7 +22971,7 @@
           <t>K | 299呎 (1房)
 $852万
 $28,511/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -22979,7 +22979,7 @@
           <t>L | 302呎 (1房)
 $934万
 $30,924/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -22987,7 +22987,7 @@
           <t>M | 293呎 (1房)
 $939万
 $32,059/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -22995,7 +22995,7 @@
           <t>N | 300呎 (1房)
 $938万
 $31,283/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -23018,7 +23018,7 @@
           <t>B | 286呎 (1房)
 $903万
 $31,563/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -23026,7 +23026,7 @@
           <t>C | 456呎 (2房)
 $1365万
 $29,928/呎
-(21年-12月)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -23034,7 +23034,7 @@
           <t>D | 332呎 (1房)
 $1019万
 $30,679/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -23050,7 +23050,7 @@
           <t>F | 265呎 (开放式)
 $804万
 $30,353/呎
-(22年-03月)</t>
+(22年-03月-08日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -23058,7 +23058,7 @@
           <t>G | 292呎 (1房)
 $875万
 $29,965/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -23066,7 +23066,7 @@
           <t>H | 228呎 (开放式)
 $726万
 $31,839/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -23074,7 +23074,7 @@
           <t>J | 288呎 (1房)
 $841万
 $29,203/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -23082,7 +23082,7 @@
           <t>K | 298呎 (1房)
 $830万
 $27,846/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -23090,7 +23090,7 @@
           <t>L | 302呎 (1房)
 $909万
 $30,108/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -23098,7 +23098,7 @@
           <t>M | 293呎 (1房)
 $935万
 $31,899/呎
-(23年-12月)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -23106,7 +23106,7 @@
           <t>N | 300呎 (1房)
 $934万
 $31,130/呎
-(21年-12月)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
           <t>B | 287呎 (1房)
 $898万
 $31,302/呎
-(23年-05月)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -23137,7 +23137,7 @@
           <t>C | 456呎 (2房)
 $1391万
 $30,511/呎
-(22年-02月)</t>
+(22年-02月-13日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -23145,7 +23145,7 @@
           <t>D | 332呎 (1房)
 $1013万
 $30,526/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -23153,7 +23153,7 @@
           <t>E | 262呎 (开放式)
 $779万
 $29,717/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -23161,7 +23161,7 @@
           <t>F | 265呎 (开放式)
 $796万
 $30,054/呎
-(21年-11月)</t>
+(21年-11月-19日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -23169,7 +23169,7 @@
           <t>G | 292呎 (1房)
 $866万
 $29,641/呎
-(23年-05月)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -23177,7 +23177,7 @@
           <t>H | 228呎 (开放式)
 $711万
 $31,164/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -23185,7 +23185,7 @@
           <t>J | 288呎 (1房)
 $819万
 $28,428/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -23193,7 +23193,7 @@
           <t>K | 298呎 (1房)
 $826万
 $27,710/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -23201,7 +23201,7 @@
           <t>L | 302呎 (1房)
 $925万
 $30,634/呎
-(21年-12月)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -23209,7 +23209,7 @@
           <t>M | 292呎 (1房)
 $941万
 $32,219/呎
-(23年-05月)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -23217,7 +23217,7 @@
           <t>N | 301呎 (1房)
 $929万
 $30,870/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -23240,7 +23240,7 @@
           <t>B | 287呎 (1房)
 $894万
 $31,149/呎
-(23年-06月)</t>
+(23年-06月-06日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -23248,7 +23248,7 @@
           <t>C | 456呎 (2房)
 $1367万
 $29,975/呎
-(22年-01月)</t>
+(22年-01月-16日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -23256,7 +23256,7 @@
           <t>D | 332呎 (1房)
 $1008万
 $30,374/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -23264,7 +23264,7 @@
           <t>E | 262呎 (开放式)
 $775万
 $29,569/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -23272,7 +23272,7 @@
           <t>F | 265呎 (开放式)
 $792万
 $29,905/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -23280,7 +23280,7 @@
           <t>G | 292呎 (1房)
 $861万
 $29,497/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -23288,7 +23288,7 @@
           <t>H | 228呎 (开放式)
 $687万
 $30,146/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -23296,7 +23296,7 @@
           <t>J | 288呎 (1房)
 $833万
 $28,916/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -23304,7 +23304,7 @@
           <t>K | 298呎 (1房)
 $840万
 $28,183/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -23312,7 +23312,7 @@
           <t>L | 302呎 (1房)
 $921万
 $30,488/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -23320,7 +23320,7 @@
           <t>M | 293呎 (1房)
 $916万
 $31,254/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23328,7 +23328,7 @@
           <t>N | 301呎 (1房)
 $925万
 $30,718/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -23351,7 +23351,7 @@
           <t>B | 287呎 (1房)
 $885万
 $30,826/呎
-(22年-04月)</t>
+(22年-04月-19日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -23359,7 +23359,7 @@
           <t>C | 456呎 (2房)
 $1323万
 $29,015/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -23367,7 +23367,7 @@
           <t>D | 332呎 (1房)
 $992万
 $29,865/呎
-(21年-12月)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -23375,7 +23375,7 @@
           <t>E | 262呎 (开放式)
 $771万
 $29,422/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -23383,7 +23383,7 @@
           <t>F | 264呎 (开放式)
 $771万
 $29,219/呎
-(21年-12月)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -23391,7 +23391,7 @@
           <t>G | 292呎 (1房)
 $857万
 $29,349/呎
-(22年-06月)</t>
+(22年-06月-08日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -23399,7 +23399,7 @@
           <t>H | 228呎 (开放式)
 $684万
 $29,996/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -23407,7 +23407,7 @@
           <t>J | 288呎 (1房)
 $829万
 $28,769/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -23415,7 +23415,7 @@
           <t>K | 299呎 (1房)
 $836万
 $27,947/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -23423,7 +23423,7 @@
           <t>L | 302呎 (1房)
 $867万
 $28,721/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -23431,7 +23431,7 @@
           <t>M | 293呎 (1房)
 $888万
 $30,311/呎
-(24年-02月)</t>
+(24年-02月-28日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23439,7 +23439,7 @@
           <t>N | 300呎 (1房)
 $907万
 $30,231/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -23462,7 +23462,7 @@
           <t>B | 287呎 (1房)
 $883万
 $30,767/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -23470,7 +23470,7 @@
           <t>C | 456呎 (2房)
 $1294万
 $28,370/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -23478,7 +23478,7 @@
           <t>D | 332呎 (1房)
 $989万
 $29,797/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -23486,7 +23486,7 @@
           <t>E | 262呎 (开放式)
 $767万
 $29,277/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -23494,7 +23494,7 @@
           <t>F | 265呎 (开放式)
 $785万
 $29,610/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -23502,7 +23502,7 @@
           <t>G | 292呎 (1房)
 $872万
 $29,853/呎
-(22年-06月)</t>
+(22年-06月-07日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -23510,7 +23510,7 @@
           <t>H | 228呎 (开放式)
 $680万
 $29,846/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -23518,7 +23518,7 @@
           <t>J | 288呎 (1房)
 $824万
 $28,628/呎
-(21年-12月)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -23526,7 +23526,7 @@
           <t>K | 298呎 (1房)
 $831万
 $27,902/呎
-(21年-12月)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -23534,7 +23534,7 @@
           <t>L | 302呎 (1房)
 $846万
 $28,017/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -23542,7 +23542,7 @@
           <t>M | 293呎 (1房)
 $870万
 $29,706/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -23550,7 +23550,7 @@
           <t>N | 301呎 (1房)
 $894万
 $29,690/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -23573,7 +23573,7 @@
           <t>B | 287呎 (1房)
 $879万
 $30,616/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -23581,7 +23581,7 @@
           <t>C | 456呎 (2房)
 $1290万
 $28,285/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -23589,7 +23589,7 @@
           <t>D | 332呎 (1房)
 $953万
 $28,705/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -23597,7 +23597,7 @@
           <t>E | 262呎 (开放式)
 $801万
 $30,586/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -23605,7 +23605,7 @@
           <t>F | 264呎 (开放式)
 $764万
 $28,930/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -23613,7 +23613,7 @@
           <t>G | 292呎 (1房)
 $863万
 $29,540/呎
-(23年-12月)</t>
+(23年-12月-13日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -23621,7 +23621,7 @@
           <t>H | 228呎 (开放式)
 $677万
 $29,700/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -23629,7 +23629,7 @@
           <t>J | 288呎 (1房)
 $802万
 $27,847/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -23637,7 +23637,7 @@
           <t>K | 298呎 (1房)
 $809万
 $27,142/呎
-(21年-11月)</t>
+(21年-11月-19日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -23645,7 +23645,7 @@
           <t>L | 302呎 (1房)
 $842万
 $27,877/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -23653,7 +23653,7 @@
           <t>M | 293呎 (1房)
 $866万
 $29,559/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -23661,7 +23661,7 @@
           <t>N | 301呎 (1房)
 $870万
 $28,902/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -23684,7 +23684,7 @@
           <t>B | 287呎 (1房)
 $874万
 $30,469/呎
-(21年-11月)</t>
+(21年-11月-27日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -23692,7 +23692,7 @@
           <t>C | 456呎 (2房)
 $1354万
 $29,692/呎
-(22年-05月)</t>
+(22年-05月-24日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -23700,7 +23700,7 @@
           <t>D | 332呎 (1房)
 $969万
 $29,199/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -23708,7 +23708,7 @@
           <t>E | 262呎 (开放式)
 $797万
 $30,435/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -23716,7 +23716,7 @@
           <t>F | 264呎 (开放式)
 $777万
 $29,426/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -23724,7 +23724,7 @@
           <t>G | 292呎 (1房)
 $844万
 $28,911/呎
-(23年-08月)</t>
+(23年-08月-21日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -23732,7 +23732,7 @@
           <t>H | 228呎 (开放式)
 $674万
 $29,550/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -23740,7 +23740,7 @@
           <t>J | 288呎 (1房)
 $816万
 $28,325/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -23748,7 +23748,7 @@
           <t>K | 299呎 (1房)
 $823万
 $27,517/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -23756,7 +23756,7 @@
           <t>L | 302呎 (1房)
 $820万
 $27,137/呎
-(21年-11月)</t>
+(21年-11月-19日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -23764,7 +23764,7 @@
           <t>M | 293呎 (1房)
 $862万
 $29,411/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -23772,7 +23772,7 @@
           <t>N | 300呎 (1房)
 $885万
 $29,495/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -23795,7 +23795,7 @@
           <t>B | 287呎 (1房)
 $855万
 $29,807/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -23803,7 +23803,7 @@
           <t>C | 456呎 (2房)
 $1354万
 $29,692/呎
-(22年-08月)</t>
+(22年-08月-16日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -23811,7 +23811,7 @@
           <t>D | 332呎 (1房)
 $969万
 $29,199/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -23819,7 +23819,7 @@
           <t>E | 262呎 (开放式)
 $797万
 $30,435/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -23827,7 +23827,7 @@
           <t>F | 264呎 (开放式)
 $777万
 $29,426/呎
-(21年-12月)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -23835,7 +23835,7 @@
           <t>G | 292呎 (1房)
 $844万
 $28,911/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -23843,7 +23843,7 @@
           <t>H | 228呎 (开放式)
 $694万
 $30,438/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -23851,7 +23851,7 @@
           <t>J | 288呎 (1房)
 $816万
 $28,325/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -23859,7 +23859,7 @@
           <t>K | 298呎 (1房)
 $823万
 $27,609/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -23867,7 +23867,7 @@
           <t>L | 302呎 (1房)
 $838万
 $27,740/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -23875,7 +23875,7 @@
           <t>M | 293呎 (1房)
 $862万
 $29,411/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -23883,7 +23883,7 @@
           <t>N | 301呎 (1房)
 $885万
 $29,397/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -23906,7 +23906,7 @@
           <t>B | 286呎 (1房)
 $844万
 $29,523/呎
-(21年-12月)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -23914,7 +23914,7 @@
           <t>C | 456呎 (2房)
 $1313万
 $28,788/呎
-(23年-02月)</t>
+(23年-02月-21日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -23922,7 +23922,7 @@
           <t>D | 332呎 (1房)
 $965万
 $29,071/呎
-(21年-12月)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -23930,7 +23930,7 @@
           <t>E | 262呎 (开放式)
 $786万
 $29,992/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -23938,7 +23938,7 @@
           <t>F | 264呎 (开放式)
 $746万
 $28,264/呎
-(23年-04月)</t>
+(23年-04月-12日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -23946,7 +23946,7 @@
           <t>G | 292呎 (1房)
 $816万
 $27,949/呎
-(22年-08月)</t>
+(22年-08月-16日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -23954,7 +23954,7 @@
           <t>H | 228呎 (开放式)
 $664万
 $29,112/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -23962,7 +23962,7 @@
           <t>J | 288呎 (1房)
 $789万
 $27,408/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -23970,7 +23970,7 @@
           <t>K | 299呎 (1房)
 $810万
 $27,104/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -23978,7 +23978,7 @@
           <t>L | 302呎 (1房)
 $825万
 $27,326/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -23986,7 +23986,7 @@
           <t>M | 293呎 (1房)
 $824万
 $28,115/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -23994,7 +23994,7 @@
           <t>N | 301呎 (1房)
 $855万
 $28,398/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
           <t>B | 287呎 (1房)
 $822万
 $28,637/呎
-(21年-12月)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -24025,7 +24025,7 @@
           <t>C | 456呎 (2房)
 $1309万
 $28,703/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -24033,7 +24033,7 @@
           <t>D | 332呎 (1房)
 $950万
 $28,620/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -24041,7 +24041,7 @@
           <t>E | 262呎 (开放式)
 $730万
 $27,859/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -24049,7 +24049,7 @@
           <t>F | 265呎 (开放式)
 $730万
 $27,557/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -24057,7 +24057,7 @@
           <t>G | 292呎 (1房)
 $812万
 $27,811/呎
-(23年-04月)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -24065,7 +24065,7 @@
           <t>H | 228呎 (开放式)
 $646万
 $28,354/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -24073,7 +24073,7 @@
           <t>J | 288呎 (1房)
 $785万
 $27,271/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -24081,7 +24081,7 @@
           <t>K | 299呎 (1房)
 $806万
 $26,969/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -24089,7 +24089,7 @@
           <t>L | 302呎 (1房)
 $821万
 $27,189/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -24097,7 +24097,7 @@
           <t>M | 293呎 (1房)
 $835万
 $28,499/呎
-(24年-02月)</t>
+(24年-02月-18日)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -24105,7 +24105,7 @@
           <t>N | 300呎 (1房)
 $850万
 $28,348/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -24128,7 +24128,7 @@
           <t>B | 287呎 (1房)
 $818万
 $28,493/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -24136,7 +24136,7 @@
           <t>C | 456呎 (2房)
 $1295万
 $28,399/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -24144,7 +24144,7 @@
           <t>D | 332呎 (1房)
 $945万
 $28,476/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -24152,7 +24152,7 @@
           <t>E | 262呎 (开放式)
 $789万
 $30,116/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -24160,7 +24160,7 @@
           <t>F | 265呎 (开放式)
 $743万
 $28,030/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -24168,7 +24168,7 @@
           <t>G | 292呎 (1房)
 $808万
 $27,672/呎
-(23年-03月)</t>
+(23年-03月-21日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -24176,7 +24176,7 @@
           <t>H | 228呎 (开放式)
 $644万
 $28,255/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -24184,7 +24184,7 @@
           <t>J | 288呎 (1房)
 $781万
 $27,133/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -24192,7 +24192,7 @@
           <t>K | 298呎 (1房)
 $802万
 $26,924/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -24200,7 +24200,7 @@
           <t>L | 302呎 (1房)
 $799万
 $26,467/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -24208,7 +24208,7 @@
           <t>M | 293呎 (1房)
 $819万
 $27,949/呎
-(23年-05月)</t>
+(23年-05月-29日)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -24216,7 +24216,7 @@
           <t>N | 301呎 (1房)
 $846万
 $28,113/呎
-(21年-12月)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -24239,7 +24239,7 @@
           <t>B | 286呎 (1房)
 $832万
 $29,083/呎
-(21年-12月)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -24247,7 +24247,7 @@
           <t>C | 456呎 (2房)
 $1291万
 $28,312/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -24255,7 +24255,7 @@
           <t>D | 333呎 (1房)
 $951万
 $28,556/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -24263,7 +24263,7 @@
           <t>E | 262呎 (开放式)
 $723万
 $27,581/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -24271,7 +24271,7 @@
           <t>F | 265呎 (开放式)
 $739万
 $27,888/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -24279,7 +24279,7 @@
           <t>G | 292呎 (1房)
 $804万
 $27,533/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -24287,7 +24287,7 @@
           <t>H | 228呎 (开放式)
 $640万
 $28,069/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -24295,7 +24295,7 @@
           <t>J | 288呎 (1房)
 $778万
 $26,999/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -24303,7 +24303,7 @@
           <t>K | 298呎 (1房)
 $798万
 $26,791/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -24311,7 +24311,7 @@
           <t>L | 302呎 (1房)
 $813万
 $26,918/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
@@ -24319,7 +24319,7 @@
           <t>M | 293呎 (1房)
 $819万
 $27,940/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -24327,7 +24327,7 @@
           <t>N | 301呎 (1房)
 $842万
 $27,973/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -24350,7 +24350,7 @@
           <t>B | 287呎 (1房)
 $828万
 $28,837/呎
-(21年-12月)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -24358,7 +24358,7 @@
           <t>C | 456呎 (2房)
 $1287万
 $28,227/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -24366,7 +24366,7 @@
           <t>D | 333呎 (1房)
 $916万
 $27,497/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -24374,7 +24374,7 @@
           <t>E | 262呎 (开放式)
 $735万
 $28,053/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -24382,7 +24382,7 @@
           <t>F | 265呎 (开放式)
 $719万
 $27,146/呎
-(21年-11月)</t>
+(21年-11月-19日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -24390,7 +24390,7 @@
           <t>G | 292呎 (1房)
 $800万
 $27,395/呎
-(23年-06月)</t>
+(23年-06月-18日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -24398,7 +24398,7 @@
           <t>H | 228呎 (开放式)
 $652万
 $28,596/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -24406,7 +24406,7 @@
           <t>J | 288呎 (1房)
 $774万
 $26,865/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -24414,7 +24414,7 @@
           <t>K | 298呎 (1房)
 $794万
 $26,655/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -24422,7 +24422,7 @@
           <t>L | 302呎 (1房)
 $809万
 $26,783/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -24430,7 +24430,7 @@
           <t>M | 292呎 (1房)
 $814万
 $27,875/呎
-(23年-09月)</t>
+(23年-09月-04日)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -24438,7 +24438,7 @@
           <t>N | 300呎 (1房)
 $838万
 $27,925/呎
-(21年-12月)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
           <t>B | 286呎 (1房)
 $815万
 $28,510/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -24469,7 +24469,7 @@
           <t>C | 456呎 (2房)
 $1287万
 $28,220/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -24477,7 +24477,7 @@
           <t>D | 333呎 (1房)
 $927万
 $27,829/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -24485,7 +24485,7 @@
           <t>E | 262呎 (开放式)
 $715万
 $27,306/呎
-(26年-01月)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -24493,7 +24493,7 @@
           <t>F | 264呎 (开放式)
 $732万
 $27,715/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -24501,7 +24501,7 @@
           <t>G | 292呎 (1房)
 $796万
 $27,259/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -24509,7 +24509,7 @@
           <t>H | 229呎 (开放式)
 $649万
 $28,327/呎
-(21年-12月)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -24517,7 +24517,7 @@
           <t>J | 288呎 (1房)
 $770万
 $26,728/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -24525,7 +24525,7 @@
           <t>K | 299呎 (1房)
 $790万
 $26,434/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -24533,7 +24533,7 @@
           <t>L | 302呎 (1房)
 $805万
 $26,649/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -24541,7 +24541,7 @@
           <t>M | 293呎 (1房)
 $804万
 $27,424/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -24549,7 +24549,7 @@
           <t>N | 300呎 (1房)
 $825万
 $27,511/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -24572,7 +24572,7 @@
           <t>B | 286呎 (1房)
 $815万
 $28,510/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -24580,7 +24580,7 @@
           <t>C | 456呎 (2房)
 $1287万
 $28,220/呎
-(23年-03月)</t>
+(23年-03月-19日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -24588,7 +24588,7 @@
           <t>D | 332呎 (1房)
 $927万
 $27,913/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr">
@@ -24604,7 +24604,7 @@
           <t>F | 264呎 (开放式)
 $732万
 $27,715/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -24612,7 +24612,7 @@
           <t>G | 292呎 (1房)
 $752万
 $25,761/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -24620,7 +24620,7 @@
           <t>H | 228呎 (开放式)
 $649万
 $28,451/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -24628,7 +24628,7 @@
           <t>J | 288呎 (1房)
 $770万
 $26,728/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -24636,7 +24636,7 @@
           <t>K | 298呎 (1房)
 $790万
 $26,522/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -24644,7 +24644,7 @@
           <t>L | 302呎 (1房)
 $805万
 $26,649/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr">
@@ -24652,7 +24652,7 @@
           <t>M | 293呎 (1房)
 $804万
 $27,424/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -24660,7 +24660,7 @@
           <t>N | 301呎 (1房)
 $825万
 $27,420/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -24683,7 +24683,7 @@
           <t>B | 286呎 (1房)
 $807万
 $28,227/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -24691,7 +24691,7 @@
           <t>C | 456呎 (2房)
 $1311万
 $28,747/呎
-(23年-04月)</t>
+(23年-04月-11日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -24699,7 +24699,7 @@
           <t>D | 333呎 (1房)
 $908万
 $27,254/呎
-(24年-12月)</t>
+(24年-12月-22日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -24707,7 +24707,7 @@
           <t>E | 262呎 (开放式)
 $701万
 $26,766/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -24715,7 +24715,7 @@
           <t>F | 265呎 (开放式)
 $724万
 $27,336/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -24723,7 +24723,7 @@
           <t>G | 292呎 (1房)
 $761万
 $26,072/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -24731,7 +24731,7 @@
           <t>H | 229呎 (开放式)
 $628万
 $27,436/呎
-(23年-05月)</t>
+(23年-05月-09日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -24739,7 +24739,7 @@
           <t>J | 288呎 (1房)
 $762万
 $26,462/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
@@ -24747,7 +24747,7 @@
           <t>K | 298呎 (1房)
 $782万
 $26,257/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -24755,7 +24755,7 @@
           <t>L | 302呎 (1房)
 $797万
 $26,384/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
@@ -24763,7 +24763,7 @@
           <t>M | 293呎 (1房)
 $799万
 $27,258/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24771,7 +24771,7 @@
           <t>N | 301呎 (1房)
 $817万
 $27,148/呎
-(21年-12月)</t>
+(21年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -24794,7 +24794,7 @@
           <t>B | 286呎 (1房)
 $804万
 $28,118/呎
-(21年-12月)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -24802,7 +24802,7 @@
           <t>C | 456呎 (2房)
 $1265万
 $27,739/呎
-(23年-03月)</t>
+(23年-03月-16日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -24810,7 +24810,7 @@
           <t>D | 332呎 (1房)
 $914万
 $27,533/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="F28" s="25" t="inlineStr">
@@ -24826,7 +24826,7 @@
           <t>F | 264呎 (开放式)
 $721万
 $27,300/呎
-(22年-04月)</t>
+(22年-04月-28日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -24834,7 +24834,7 @@
           <t>G | 292呎 (1房)
 $758万
 $25,942/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -24842,7 +24842,7 @@
           <t>H | 229呎 (开放式)
 $638万
 $27,881/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -24850,7 +24850,7 @@
           <t>J | 288呎 (1房)
 $742万
 $25,759/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="K28" s="20" t="inlineStr">
@@ -24858,7 +24858,7 @@
           <t>K | 299呎 (1房)
 $762万
 $25,474/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -24866,7 +24866,7 @@
           <t>L | 302呎 (1房)
 $793万
 $26,253/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="M28" s="20" t="inlineStr">
@@ -24874,7 +24874,7 @@
           <t>M | 293呎 (1房)
 $810万
 $27,631/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -24882,7 +24882,7 @@
           <t>N | 300呎 (1房)
 $813万
 $27,100/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -24905,7 +24905,7 @@
           <t>B | 287呎 (1房)
 $781万
 $27,226/呎
-(21年-12月)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -24913,7 +24913,7 @@
           <t>C | 456呎 (2房)
 $1248万
 $27,368/呎
-(22年-01月)</t>
+(22年-01月-16日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -24921,7 +24921,7 @@
           <t>D | 333呎 (1房)
 $898万
 $26,981/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -24929,7 +24929,7 @@
           <t>E | 262呎 (开放式)
 $709万
 $27,063/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -24937,7 +24937,7 @@
           <t>F | 265呎 (开放式)
 $701万
 $26,446/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -24945,7 +24945,7 @@
           <t>G | 292呎 (1房)
 $753万
 $25,785/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -24953,7 +24953,7 @@
           <t>H | 228呎 (开放式)
 $635万
 $27,834/呎
-(22年-09月)</t>
+(22年-09月-19日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -24961,7 +24961,7 @@
           <t>J | 288呎 (1房)
 $754万
 $26,172/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -24969,7 +24969,7 @@
           <t>K | 299呎 (1房)
 $757万
 $25,320/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="L29" s="20" t="inlineStr">
@@ -24977,7 +24977,7 @@
           <t>L | 302呎 (1房)
 $788万
 $26,095/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr">
@@ -24985,7 +24985,7 @@
           <t>M | 293呎 (1房)
 $794万
 $27,095/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24993,7 +24993,7 @@
           <t>N | 300呎 (1房)
 $809万
 $26,965/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
           <t>B | 286呎 (1房)
 $778万
 $27,217/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -25024,7 +25024,7 @@
           <t>C | 456呎 (2房)
 $1248万
 $27,365/呎
-(23年-06月)</t>
+(23年-06月-18日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -25032,7 +25032,7 @@
           <t>D | 333呎 (1房)
 $894万
 $26,846/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -25040,7 +25040,7 @@
           <t>E | 262呎 (开放式)
 $690万
 $26,340/呎
-(23年-08月)</t>
+(23年-08月-10日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -25048,7 +25048,7 @@
           <t>F | 265呎 (开放式)
 $697万
 $26,314/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -25056,7 +25056,7 @@
           <t>G | 292呎 (1房)
 $750万
 $25,675/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -25064,7 +25064,7 @@
           <t>H | 229呎 (开放式)
 $632万
 $27,600/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -25072,7 +25072,7 @@
           <t>J | 288呎 (1房)
 $750万
 $26,041/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="K30" s="20" t="inlineStr">
@@ -25080,7 +25080,7 @@
           <t>K | 298呎 (1房)
 $770万
 $25,840/呎
-(21年-12月)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="L30" s="20" t="inlineStr">
@@ -25088,7 +25088,7 @@
           <t>L | 302呎 (1房)
 $784万
 $25,964/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="M30" s="20" t="inlineStr">
@@ -25096,7 +25096,7 @@
           <t>M | 293呎 (1房)
 $792万
 $27,015/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
@@ -25104,7 +25104,7 @@
           <t>N | 300呎 (1房)
 $805万
 $26,830/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
           <t>C | 309呎 (1房)
 $947万
 $30,638/呎
-(23年-03月)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -25143,7 +25143,7 @@
           <t>D | 240呎 (开放式)
 $756万
 $31,502/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -25151,7 +25151,7 @@
           <t>E | 243呎 (开放式)
 $804万
 $33,100/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -25159,7 +25159,7 @@
           <t>F | 270呎 (1房)
 $814万
 $30,130/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -25167,7 +25167,7 @@
           <t>G | 207呎 (开放式)
 $637万
 $30,765/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -25175,7 +25175,7 @@
           <t>H | 267呎 (1房)
 $763万
 $28,561/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -25183,7 +25183,7 @@
           <t>J | 278呎 (1房)
 $802万
 $28,861/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -25191,7 +25191,7 @@
           <t>K | 279呎 (1房)
 $859万
 $30,799/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="L31" s="20" t="inlineStr">
@@ -25199,7 +25199,7 @@
           <t>L | 271呎 (1房)
 $964万
 $35,587/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="M31" s="20" t="inlineStr">
@@ -25207,7 +25207,7 @@
           <t>M | 279呎 (1房)
 $904万
 $32,400/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr"/>
